--- a/historial.xlsx
+++ b/historial.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>DNI</t>
   </si>
@@ -38,106 +38,79 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>12345678</t>
-  </si>
-  <si>
-    <t>Juan Perez</t>
+    <t>73494885</t>
+  </si>
+  <si>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>2028-10-04</t>
+  </si>
+  <si>
+    <t>902432263</t>
+  </si>
+  <si>
+    <t>freed.258258@gmail.com</t>
+  </si>
+  <si>
+    <t>Jr. Migueel Grau</t>
+  </si>
+  <si>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>73494886</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Ronald</t>
+  </si>
+  <si>
+    <t>902432264</t>
+  </si>
+  <si>
+    <t>Jr. Santos Bravo</t>
+  </si>
+  <si>
+    <t>12345679</t>
+  </si>
+  <si>
+    <t>Karla</t>
+  </si>
+  <si>
+    <t>Inga Galvez</t>
+  </si>
+  <si>
+    <t>2002-10-05</t>
   </si>
   <si>
     <t>987654321</t>
   </si>
   <si>
-    <t>juan@gmail.com</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>73494885</t>
-  </si>
-  <si>
-    <t>Erick</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>2028-10-04</t>
-  </si>
-  <si>
-    <t>902432263</t>
-  </si>
-  <si>
-    <t>freed.258258@gmail.com</t>
-  </si>
-  <si>
-    <t>Jr. Migueel Grau</t>
-  </si>
-  <si>
-    <t>73494884</t>
-  </si>
-  <si>
-    <t>Erick Alexander</t>
-  </si>
-  <si>
-    <t>Bruno Lzaro</t>
-  </si>
-  <si>
-    <t>2004-10-04</t>
-  </si>
-  <si>
-    <t>Jr. Miguel Grau</t>
-  </si>
-  <si>
-    <t>88888888</t>
-  </si>
-  <si>
-    <t>Jair</t>
-  </si>
-  <si>
-    <t>De La Cruz</t>
-  </si>
-  <si>
-    <t>2010-10-05</t>
-  </si>
-  <si>
-    <t>999999999</t>
-  </si>
-  <si>
-    <t>jair@gmail.com</t>
-  </si>
-  <si>
-    <t>Jr. Santos S/N, Junin</t>
-  </si>
-  <si>
-    <t>73494886</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>Ronald</t>
-  </si>
-  <si>
-    <t>902432264</t>
-  </si>
-  <si>
-    <t>Jr. Santos Bravo</t>
-  </si>
-  <si>
-    <t>12345679</t>
-  </si>
-  <si>
-    <t>Karla</t>
-  </si>
-  <si>
-    <t>Inga Galvez</t>
-  </si>
-  <si>
-    <t>2002-10-05</t>
-  </si>
-  <si>
     <t>Jr. Atahualpa S/N</t>
+  </si>
+  <si>
+    <t>71443303</t>
+  </si>
+  <si>
+    <t>Inga</t>
+  </si>
+  <si>
+    <t>2014-01-05</t>
+  </si>
+  <si>
+    <t>917450610</t>
+  </si>
+  <si>
+    <t>karlainga@gmail.com</t>
+  </si>
+  <si>
+    <t>Jr. Mariscal Castilla S/N</t>
   </si>
 </sst>
 </file>
@@ -220,16 +193,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.53515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="8.359375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.078125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.6640625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="9.9296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="21.78515625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.0703125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="19.53515625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="11.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -266,138 +239,96 @@
       <c r="B2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>11</v>
+      </c>
       <c r="E2" t="s" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>14</v>
+      </c>
       <c r="H2" t="s" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="G3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="H7" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
